--- a/data/UoB_Agreements.xlsx
+++ b/data/UoB_Agreements.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97333\Desktop\Hawra\Cloud Computing\ITCC481\Partnership\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{09E582A5-00BC-4E30-BCAE-316ECD1635F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA21C361-DCEF-44BF-81A5-6EA0E1A84388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agreements Master Sheet" sheetId="1" r:id="rId1"/>
     <sheet name="Leaders info" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="211">
   <si>
     <t>Record ID</t>
   </si>
@@ -662,6 +661,12 @@
   </si>
   <si>
     <t>+973 17437775</t>
+  </si>
+  <si>
+    <t>Memorandum of Understanding</t>
+  </si>
+  <si>
+    <t>MoU</t>
   </si>
 </sst>
 </file>
@@ -1177,7 +1182,7 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>209</v>
       </c>
       <c r="D2" t="s">
         <v>24</v>
@@ -1316,7 +1321,7 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>209</v>
       </c>
       <c r="D4" t="s">
         <v>43</v>
@@ -1387,7 +1392,7 @@
         <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>210</v>
       </c>
       <c r="D5" t="s">
         <v>45</v>

--- a/data/UoB_Agreements.xlsx
+++ b/data/UoB_Agreements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97333\Desktop\Hawra\Cloud Computing\ITCC481\Partnership\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA21C361-DCEF-44BF-81A5-6EA0E1A84388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C33CB9-5BF1-454E-A53A-457970A2376E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="209">
   <si>
     <t>Record ID</t>
   </si>
@@ -105,9 +105,6 @@
     <t>Tamkeen</t>
   </si>
   <si>
-    <t>Memorandum of Understanding (MoU)</t>
-  </si>
-  <si>
     <t>Academic partnership focusing on student mobility, faculty exchange, and joint curriculum development.</t>
   </si>
   <si>
@@ -664,9 +661,6 @@
   </si>
   <si>
     <t>Memorandum of Understanding</t>
-  </si>
-  <si>
-    <t>MoU</t>
   </si>
 </sst>
 </file>
@@ -1159,7 +1153,7 @@
         <v>17</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>18</v>
@@ -1182,34 +1176,34 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
         <v>24</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="G2" t="s">
         <v>22</v>
       </c>
       <c r="H2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" t="s">
         <v>27</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>28</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>29</v>
       </c>
-      <c r="K2" t="s">
-        <v>30</v>
-      </c>
       <c r="L2" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M2" s="2">
         <v>43466</v>
@@ -1218,7 +1212,7 @@
         <v>44561</v>
       </c>
       <c r="O2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P2">
         <v>7</v>
@@ -1230,10 +1224,10 @@
         <v>1</v>
       </c>
       <c r="T2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="V2">
         <v>26.2285</v>
@@ -1247,37 +1241,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>35</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>36</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>37</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" t="s">
         <v>38</v>
       </c>
-      <c r="G3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" t="s">
         <v>39</v>
       </c>
-      <c r="I3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" t="s">
-        <v>40</v>
-      </c>
       <c r="L3" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M3" s="2">
         <v>44561</v>
@@ -1286,7 +1280,7 @@
         <v>45656</v>
       </c>
       <c r="O3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P3">
         <v>10</v>
@@ -1298,13 +1292,13 @@
         <v>1</v>
       </c>
       <c r="S3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="T3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V3">
         <v>26.2285</v>
@@ -1321,34 +1315,34 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" t="s">
         <v>43</v>
-      </c>
-      <c r="E4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" t="s">
-        <v>44</v>
       </c>
       <c r="G4" t="s">
         <v>22</v>
       </c>
       <c r="H4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" t="s">
         <v>27</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>28</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>29</v>
       </c>
-      <c r="K4" t="s">
-        <v>30</v>
-      </c>
       <c r="L4" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M4" s="2">
         <v>43466</v>
@@ -1357,7 +1351,7 @@
         <v>44926</v>
       </c>
       <c r="O4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P4">
         <v>7</v>
@@ -1369,13 +1363,13 @@
         <v>2</v>
       </c>
       <c r="S4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="T4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V4">
         <v>26.2285</v>
@@ -1389,37 +1383,37 @@
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" t="s">
         <v>45</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>46</v>
       </c>
-      <c r="F5" t="s">
-        <v>47</v>
-      </c>
       <c r="G5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" t="s">
         <v>39</v>
       </c>
-      <c r="I5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J5" t="s">
-        <v>29</v>
-      </c>
-      <c r="K5" t="s">
-        <v>40</v>
-      </c>
       <c r="L5" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M5" s="2">
         <v>44561</v>
@@ -1428,7 +1422,7 @@
         <v>46021</v>
       </c>
       <c r="O5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P5">
         <v>10</v>
@@ -1440,13 +1434,13 @@
         <v>2</v>
       </c>
       <c r="S5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="T5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V5">
         <v>26.2285</v>
@@ -1463,34 +1457,34 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" t="s">
         <v>48</v>
-      </c>
-      <c r="E6" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" t="s">
-        <v>49</v>
       </c>
       <c r="G6" t="s">
         <v>22</v>
       </c>
       <c r="H6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" t="s">
         <v>27</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>28</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>29</v>
       </c>
-      <c r="K6" t="s">
-        <v>30</v>
-      </c>
       <c r="L6" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M6" s="2">
         <v>43466</v>
@@ -1499,7 +1493,7 @@
         <v>45291</v>
       </c>
       <c r="O6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P6">
         <v>7</v>
@@ -1511,13 +1505,13 @@
         <v>3</v>
       </c>
       <c r="S6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V6">
         <v>26.2285</v>
@@ -1531,37 +1525,37 @@
         <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" t="s">
         <v>50</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>51</v>
       </c>
-      <c r="F7" t="s">
-        <v>52</v>
-      </c>
       <c r="G7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H7" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7" t="s">
         <v>39</v>
       </c>
-      <c r="I7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J7" t="s">
-        <v>29</v>
-      </c>
-      <c r="K7" t="s">
-        <v>40</v>
-      </c>
       <c r="L7" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M7" s="2">
         <v>44561</v>
@@ -1570,7 +1564,7 @@
         <v>46386</v>
       </c>
       <c r="O7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P7">
         <v>10</v>
@@ -1582,13 +1576,13 @@
         <v>3</v>
       </c>
       <c r="S7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V7">
         <v>26.2285</v>
@@ -1602,37 +1596,37 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" t="s">
         <v>53</v>
       </c>
-      <c r="C8" t="s">
-        <v>137</v>
-      </c>
-      <c r="D8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>54</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" t="s">
         <v>55</v>
       </c>
-      <c r="G8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>56</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>57</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>58</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
         <v>59</v>
-      </c>
-      <c r="L8" t="s">
-        <v>60</v>
       </c>
       <c r="M8" s="2">
         <v>43831</v>
@@ -1641,7 +1635,7 @@
         <v>45291</v>
       </c>
       <c r="O8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P8">
         <v>8</v>
@@ -1653,13 +1647,13 @@
         <v>2</v>
       </c>
       <c r="S8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V8">
         <v>30.0444</v>
@@ -1673,37 +1667,37 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" t="s">
         <v>64</v>
       </c>
-      <c r="F9" t="s">
-        <v>65</v>
-      </c>
       <c r="G9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I9" t="s">
         <v>56</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>57</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>58</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>59</v>
-      </c>
-      <c r="L9" t="s">
-        <v>60</v>
       </c>
       <c r="M9" s="2">
         <v>43831</v>
@@ -1712,7 +1706,7 @@
         <v>45656</v>
       </c>
       <c r="O9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P9">
         <v>8</v>
@@ -1724,13 +1718,13 @@
         <v>3</v>
       </c>
       <c r="S9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V9">
         <v>30.0444</v>
@@ -1744,37 +1738,37 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" t="s">
         <v>56</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>57</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>58</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
         <v>59</v>
-      </c>
-      <c r="L10" t="s">
-        <v>60</v>
       </c>
       <c r="M10" s="2">
         <v>43831</v>
@@ -1783,7 +1777,7 @@
         <v>44926</v>
       </c>
       <c r="O10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P10">
         <v>8</v>
@@ -1795,13 +1789,13 @@
         <v>1</v>
       </c>
       <c r="S10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V10">
         <v>30.0444</v>
@@ -1815,37 +1809,37 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" t="s">
+        <v>208</v>
+      </c>
+      <c r="D11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" t="s">
         <v>67</v>
       </c>
-      <c r="C11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I11" t="s">
         <v>68</v>
       </c>
-      <c r="G11" t="s">
-        <v>67</v>
-      </c>
-      <c r="H11" t="s">
-        <v>56</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>69</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>70</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
         <v>71</v>
-      </c>
-      <c r="L11" t="s">
-        <v>72</v>
       </c>
       <c r="M11" s="2">
         <v>43831</v>
@@ -1854,7 +1848,7 @@
         <v>45656</v>
       </c>
       <c r="O11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P11">
         <v>3</v>
@@ -1866,13 +1860,13 @@
         <v>3</v>
       </c>
       <c r="S11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V11">
         <v>51.339700000000001</v>
@@ -1886,37 +1880,37 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
+        <v>208</v>
+      </c>
+      <c r="D12" t="s">
         <v>23</v>
       </c>
-      <c r="D12" t="s">
-        <v>24</v>
-      </c>
       <c r="E12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I12" t="s">
+        <v>68</v>
+      </c>
+      <c r="J12" t="s">
         <v>69</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>70</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" t="s">
         <v>71</v>
-      </c>
-      <c r="L12" t="s">
-        <v>72</v>
       </c>
       <c r="M12" s="2">
         <v>43831</v>
@@ -1925,7 +1919,7 @@
         <v>44926</v>
       </c>
       <c r="O12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P12">
         <v>3</v>
@@ -1937,13 +1931,13 @@
         <v>1</v>
       </c>
       <c r="S12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="T12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V12">
         <v>51.339700000000001</v>
@@ -1957,37 +1951,37 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>208</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I13" t="s">
+        <v>68</v>
+      </c>
+      <c r="J13" t="s">
         <v>69</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>70</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L13" t="s">
         <v>71</v>
-      </c>
-      <c r="L13" t="s">
-        <v>72</v>
       </c>
       <c r="M13" s="2">
         <v>43831</v>
@@ -1996,7 +1990,7 @@
         <v>45291</v>
       </c>
       <c r="O13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P13">
         <v>3</v>
@@ -2008,13 +2002,13 @@
         <v>2</v>
       </c>
       <c r="S13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V13">
         <v>51.339700000000001</v>
@@ -2028,37 +2022,37 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" t="s">
+        <v>208</v>
+      </c>
+      <c r="D14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" t="s">
         <v>75</v>
       </c>
-      <c r="C14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" t="s">
-        <v>64</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
+        <v>74</v>
+      </c>
+      <c r="H14" t="s">
+        <v>55</v>
+      </c>
+      <c r="I14" t="s">
         <v>76</v>
       </c>
-      <c r="G14" t="s">
-        <v>75</v>
-      </c>
-      <c r="H14" t="s">
-        <v>56</v>
-      </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>77</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>78</v>
       </c>
-      <c r="K14" t="s">
+      <c r="L14" t="s">
         <v>79</v>
-      </c>
-      <c r="L14" t="s">
-        <v>80</v>
       </c>
       <c r="M14" s="2">
         <v>44196</v>
@@ -2067,7 +2061,7 @@
         <v>45291</v>
       </c>
       <c r="O14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P14">
         <v>4</v>
@@ -2079,13 +2073,13 @@
         <v>1</v>
       </c>
       <c r="S14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V14">
         <v>35.712800000000001</v>
@@ -2099,37 +2093,37 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>208</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I15" t="s">
+        <v>76</v>
+      </c>
+      <c r="J15" t="s">
         <v>77</v>
       </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>78</v>
       </c>
-      <c r="K15" t="s">
+      <c r="L15" t="s">
         <v>79</v>
-      </c>
-      <c r="L15" t="s">
-        <v>80</v>
       </c>
       <c r="M15" s="2">
         <v>44196</v>
@@ -2138,7 +2132,7 @@
         <v>45656</v>
       </c>
       <c r="O15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P15">
         <v>4</v>
@@ -2150,13 +2144,13 @@
         <v>2</v>
       </c>
       <c r="S15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V15">
         <v>35.712800000000001</v>
@@ -2170,37 +2164,37 @@
         <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>208</v>
       </c>
       <c r="D16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J16" t="s">
         <v>77</v>
       </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>78</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
         <v>79</v>
-      </c>
-      <c r="L16" t="s">
-        <v>80</v>
       </c>
       <c r="M16" s="2">
         <v>44196</v>
@@ -2209,7 +2203,7 @@
         <v>46021</v>
       </c>
       <c r="O16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P16">
         <v>4</v>
@@ -2221,13 +2215,13 @@
         <v>3</v>
       </c>
       <c r="S16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="T16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V16">
         <v>35.712800000000001</v>
@@ -2241,37 +2235,37 @@
         <v>2</v>
       </c>
       <c r="B17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" t="s">
+        <v>208</v>
+      </c>
+      <c r="D17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17" t="s">
         <v>85</v>
       </c>
-      <c r="C17" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" t="s">
-        <v>51</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
+        <v>84</v>
+      </c>
+      <c r="H17" t="s">
+        <v>55</v>
+      </c>
+      <c r="I17" t="s">
         <v>86</v>
       </c>
-      <c r="G17" t="s">
-        <v>85</v>
-      </c>
-      <c r="H17" t="s">
-        <v>56</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>87</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>88</v>
       </c>
-      <c r="K17" t="s">
+      <c r="L17" t="s">
         <v>89</v>
-      </c>
-      <c r="L17" t="s">
-        <v>90</v>
       </c>
       <c r="M17" s="2">
         <v>43466</v>
@@ -2280,7 +2274,7 @@
         <v>44926</v>
       </c>
       <c r="O17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P17">
         <v>2</v>
@@ -2292,13 +2286,13 @@
         <v>2</v>
       </c>
       <c r="S17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V17">
         <v>3.1318999999999999</v>
@@ -2312,37 +2306,37 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>208</v>
       </c>
       <c r="D18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E18" t="s">
+        <v>90</v>
+      </c>
+      <c r="F18" t="s">
         <v>91</v>
       </c>
-      <c r="F18" t="s">
-        <v>92</v>
-      </c>
       <c r="G18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I18" t="s">
+        <v>86</v>
+      </c>
+      <c r="J18" t="s">
         <v>87</v>
       </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>88</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L18" t="s">
         <v>89</v>
-      </c>
-      <c r="L18" t="s">
-        <v>90</v>
       </c>
       <c r="M18" s="2">
         <v>43466</v>
@@ -2351,7 +2345,7 @@
         <v>45291</v>
       </c>
       <c r="O18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P18">
         <v>2</v>
@@ -2363,13 +2357,13 @@
         <v>3</v>
       </c>
       <c r="S18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V18">
         <v>3.1318999999999999</v>
@@ -2383,37 +2377,37 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>208</v>
       </c>
       <c r="D19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G19" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I19" t="s">
+        <v>86</v>
+      </c>
+      <c r="J19" t="s">
         <v>87</v>
       </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>88</v>
       </c>
-      <c r="K19" t="s">
+      <c r="L19" t="s">
         <v>89</v>
-      </c>
-      <c r="L19" t="s">
-        <v>90</v>
       </c>
       <c r="M19" s="2">
         <v>43466</v>
@@ -2422,7 +2416,7 @@
         <v>44561</v>
       </c>
       <c r="O19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P19">
         <v>2</v>
@@ -2434,13 +2428,13 @@
         <v>1</v>
       </c>
       <c r="S19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V19">
         <v>3.1318999999999999</v>
@@ -2454,37 +2448,37 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" t="s">
+        <v>208</v>
+      </c>
+      <c r="D20" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20" t="s">
         <v>94</v>
       </c>
-      <c r="C20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" t="s">
-        <v>51</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
+        <v>93</v>
+      </c>
+      <c r="H20" t="s">
+        <v>55</v>
+      </c>
+      <c r="I20" t="s">
         <v>95</v>
       </c>
-      <c r="G20" t="s">
-        <v>94</v>
-      </c>
-      <c r="H20" t="s">
-        <v>56</v>
-      </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
         <v>96</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>97</v>
       </c>
-      <c r="K20" t="s">
+      <c r="L20" t="s">
         <v>98</v>
-      </c>
-      <c r="L20" t="s">
-        <v>99</v>
       </c>
       <c r="M20" s="2">
         <v>44196</v>
@@ -2493,7 +2487,7 @@
         <v>46021</v>
       </c>
       <c r="O20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P20">
         <v>9</v>
@@ -2505,13 +2499,13 @@
         <v>3</v>
       </c>
       <c r="S20" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="T20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V20">
         <v>25.354800000000001</v>
@@ -2525,37 +2519,37 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s">
+        <v>208</v>
+      </c>
+      <c r="D21" t="s">
         <v>23</v>
       </c>
-      <c r="D21" t="s">
-        <v>24</v>
-      </c>
       <c r="E21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I21" t="s">
+        <v>95</v>
+      </c>
+      <c r="J21" t="s">
         <v>96</v>
       </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>97</v>
       </c>
-      <c r="K21" t="s">
+      <c r="L21" t="s">
         <v>98</v>
-      </c>
-      <c r="L21" t="s">
-        <v>99</v>
       </c>
       <c r="M21" s="2">
         <v>44196</v>
@@ -2564,7 +2558,7 @@
         <v>45291</v>
       </c>
       <c r="O21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P21">
         <v>9</v>
@@ -2576,13 +2570,13 @@
         <v>1</v>
       </c>
       <c r="S21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V21">
         <v>25.354800000000001</v>
@@ -2596,37 +2590,37 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s">
-        <v>23</v>
+        <v>208</v>
       </c>
       <c r="D22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G22" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I22" t="s">
+        <v>95</v>
+      </c>
+      <c r="J22" t="s">
         <v>96</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>97</v>
       </c>
-      <c r="K22" t="s">
+      <c r="L22" t="s">
         <v>98</v>
-      </c>
-      <c r="L22" t="s">
-        <v>99</v>
       </c>
       <c r="M22" s="2">
         <v>44196</v>
@@ -2635,7 +2629,7 @@
         <v>45656</v>
       </c>
       <c r="O22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P22">
         <v>9</v>
@@ -2647,13 +2641,13 @@
         <v>2</v>
       </c>
       <c r="S22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V22">
         <v>25.354800000000001</v>
@@ -2667,37 +2661,37 @@
         <v>5</v>
       </c>
       <c r="B23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" t="s">
+        <v>208</v>
+      </c>
+      <c r="D23" t="s">
+        <v>42</v>
+      </c>
+      <c r="E23" t="s">
+        <v>90</v>
+      </c>
+      <c r="F23" t="s">
         <v>102</v>
       </c>
-      <c r="C23" t="s">
-        <v>23</v>
-      </c>
-      <c r="D23" t="s">
-        <v>43</v>
-      </c>
-      <c r="E23" t="s">
-        <v>91</v>
-      </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
+        <v>101</v>
+      </c>
+      <c r="H23" t="s">
+        <v>38</v>
+      </c>
+      <c r="I23" t="s">
         <v>103</v>
       </c>
-      <c r="G23" t="s">
-        <v>102</v>
-      </c>
-      <c r="H23" t="s">
-        <v>39</v>
-      </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>104</v>
       </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>105</v>
       </c>
-      <c r="K23" t="s">
+      <c r="L23" t="s">
         <v>106</v>
-      </c>
-      <c r="L23" t="s">
-        <v>107</v>
       </c>
       <c r="M23" s="2">
         <v>44561</v>
@@ -2706,7 +2700,7 @@
         <v>46021</v>
       </c>
       <c r="O23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P23">
         <v>5</v>
@@ -2718,13 +2712,13 @@
         <v>2</v>
       </c>
       <c r="S23" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V23">
         <v>51.507399999999997</v>
@@ -2738,37 +2732,37 @@
         <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C24" t="s">
-        <v>23</v>
+        <v>208</v>
       </c>
       <c r="D24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G24" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I24" t="s">
+        <v>103</v>
+      </c>
+      <c r="J24" t="s">
         <v>104</v>
       </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>105</v>
       </c>
-      <c r="K24" t="s">
+      <c r="L24" t="s">
         <v>106</v>
-      </c>
-      <c r="L24" t="s">
-        <v>107</v>
       </c>
       <c r="M24" s="2">
         <v>44561</v>
@@ -2777,7 +2771,7 @@
         <v>46386</v>
       </c>
       <c r="O24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P24">
         <v>5</v>
@@ -2789,13 +2783,13 @@
         <v>3</v>
       </c>
       <c r="S24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V24">
         <v>51.507399999999997</v>
@@ -2809,37 +2803,37 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C25" t="s">
+        <v>208</v>
+      </c>
+      <c r="D25" t="s">
         <v>23</v>
       </c>
-      <c r="D25" t="s">
-        <v>24</v>
-      </c>
       <c r="E25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I25" t="s">
+        <v>103</v>
+      </c>
+      <c r="J25" t="s">
         <v>104</v>
       </c>
-      <c r="J25" t="s">
+      <c r="K25" t="s">
         <v>105</v>
       </c>
-      <c r="K25" t="s">
+      <c r="L25" t="s">
         <v>106</v>
-      </c>
-      <c r="L25" t="s">
-        <v>107</v>
       </c>
       <c r="M25" s="2">
         <v>44561</v>
@@ -2848,7 +2842,7 @@
         <v>45656</v>
       </c>
       <c r="O25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P25">
         <v>5</v>
@@ -2860,13 +2854,13 @@
         <v>1</v>
       </c>
       <c r="S25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V25">
         <v>51.507399999999997</v>
@@ -2880,37 +2874,37 @@
         <v>1</v>
       </c>
       <c r="B26" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26" t="s">
+        <v>208</v>
+      </c>
+      <c r="D26" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" t="s">
+        <v>53</v>
+      </c>
+      <c r="F26" t="s">
         <v>110</v>
       </c>
-      <c r="C26" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" t="s">
-        <v>54</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
+        <v>109</v>
+      </c>
+      <c r="H26" t="s">
+        <v>55</v>
+      </c>
+      <c r="I26" t="s">
         <v>111</v>
       </c>
-      <c r="G26" t="s">
-        <v>110</v>
-      </c>
-      <c r="H26" t="s">
-        <v>56</v>
-      </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>112</v>
       </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
         <v>113</v>
       </c>
-      <c r="K26" t="s">
+      <c r="L26" t="s">
         <v>114</v>
-      </c>
-      <c r="L26" t="s">
-        <v>115</v>
       </c>
       <c r="M26" s="2">
         <v>43101</v>
@@ -2919,7 +2913,7 @@
         <v>44196</v>
       </c>
       <c r="O26" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P26">
         <v>1</v>
@@ -2931,13 +2925,13 @@
         <v>1</v>
       </c>
       <c r="S26" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="T26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V26">
         <v>42.350499999999997</v>
@@ -2951,37 +2945,37 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C27" t="s">
+        <v>208</v>
+      </c>
+      <c r="D27" t="s">
+        <v>49</v>
+      </c>
+      <c r="E27" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" t="s">
         <v>118</v>
       </c>
-      <c r="C27" t="s">
-        <v>23</v>
-      </c>
-      <c r="D27" t="s">
-        <v>50</v>
-      </c>
-      <c r="E27" t="s">
-        <v>46</v>
-      </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
+        <v>117</v>
+      </c>
+      <c r="H27" t="s">
         <v>119</v>
       </c>
-      <c r="G27" t="s">
-        <v>118</v>
-      </c>
-      <c r="H27" t="s">
+      <c r="I27" t="s">
+        <v>111</v>
+      </c>
+      <c r="J27" t="s">
         <v>120</v>
       </c>
-      <c r="I27" t="s">
-        <v>112</v>
-      </c>
-      <c r="J27" t="s">
+      <c r="K27" t="s">
         <v>121</v>
       </c>
-      <c r="K27" t="s">
+      <c r="L27" t="s">
         <v>122</v>
-      </c>
-      <c r="L27" t="s">
-        <v>123</v>
       </c>
       <c r="M27" s="2">
         <v>43101</v>
@@ -2990,7 +2984,7 @@
         <v>44926</v>
       </c>
       <c r="O27" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P27">
         <v>6</v>
@@ -3002,13 +2996,13 @@
         <v>3</v>
       </c>
       <c r="S27" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="T27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V27">
         <v>37.338200000000001</v>
@@ -3022,37 +3016,37 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C28" t="s">
-        <v>23</v>
+        <v>208</v>
       </c>
       <c r="D28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F28" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I28" t="s">
+        <v>111</v>
+      </c>
+      <c r="J28" t="s">
         <v>112</v>
       </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
         <v>113</v>
       </c>
-      <c r="K28" t="s">
+      <c r="L28" t="s">
         <v>114</v>
-      </c>
-      <c r="L28" t="s">
-        <v>115</v>
       </c>
       <c r="M28" s="2">
         <v>43101</v>
@@ -3061,7 +3055,7 @@
         <v>44561</v>
       </c>
       <c r="O28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P28">
         <v>1</v>
@@ -3073,13 +3067,13 @@
         <v>2</v>
       </c>
       <c r="S28" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V28">
         <v>42.350499999999997</v>
@@ -3093,37 +3087,37 @@
         <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C29" t="s">
-        <v>23</v>
+        <v>208</v>
       </c>
       <c r="D29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G29" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H29" t="s">
+        <v>119</v>
+      </c>
+      <c r="I29" t="s">
+        <v>111</v>
+      </c>
+      <c r="J29" t="s">
         <v>120</v>
       </c>
-      <c r="I29" t="s">
-        <v>112</v>
-      </c>
-      <c r="J29" t="s">
+      <c r="K29" t="s">
         <v>121</v>
       </c>
-      <c r="K29" t="s">
+      <c r="L29" t="s">
         <v>122</v>
-      </c>
-      <c r="L29" t="s">
-        <v>123</v>
       </c>
       <c r="M29" s="2">
         <v>43101</v>
@@ -3132,7 +3126,7 @@
         <v>44196</v>
       </c>
       <c r="O29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P29">
         <v>6</v>
@@ -3144,13 +3138,13 @@
         <v>1</v>
       </c>
       <c r="S29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="T29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V29">
         <v>37.338200000000001</v>
@@ -3164,37 +3158,37 @@
         <v>21</v>
       </c>
       <c r="B30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C30" t="s">
-        <v>23</v>
+        <v>208</v>
       </c>
       <c r="D30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I30" t="s">
+        <v>111</v>
+      </c>
+      <c r="J30" t="s">
         <v>112</v>
       </c>
-      <c r="J30" t="s">
+      <c r="K30" t="s">
         <v>113</v>
       </c>
-      <c r="K30" t="s">
+      <c r="L30" t="s">
         <v>114</v>
-      </c>
-      <c r="L30" t="s">
-        <v>115</v>
       </c>
       <c r="M30" s="2">
         <v>43101</v>
@@ -3203,7 +3197,7 @@
         <v>44926</v>
       </c>
       <c r="O30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P30">
         <v>1</v>
@@ -3215,13 +3209,13 @@
         <v>3</v>
       </c>
       <c r="S30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V30">
         <v>42.350499999999997</v>
@@ -3235,37 +3229,37 @@
         <v>26</v>
       </c>
       <c r="B31" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C31" t="s">
-        <v>23</v>
+        <v>208</v>
       </c>
       <c r="D31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F31" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G31" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H31" t="s">
+        <v>119</v>
+      </c>
+      <c r="I31" t="s">
+        <v>111</v>
+      </c>
+      <c r="J31" t="s">
         <v>120</v>
       </c>
-      <c r="I31" t="s">
-        <v>112</v>
-      </c>
-      <c r="J31" t="s">
+      <c r="K31" t="s">
         <v>121</v>
       </c>
-      <c r="K31" t="s">
+      <c r="L31" t="s">
         <v>122</v>
-      </c>
-      <c r="L31" t="s">
-        <v>123</v>
       </c>
       <c r="M31" s="2">
         <v>43101</v>
@@ -3274,7 +3268,7 @@
         <v>44561</v>
       </c>
       <c r="O31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P31">
         <v>6</v>
@@ -3286,13 +3280,13 @@
         <v>2</v>
       </c>
       <c r="S31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="T31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V31">
         <v>37.338200000000001</v>
@@ -3338,25 +3332,25 @@
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>141</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="G1" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.35">
@@ -3364,22 +3358,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>195</v>
-      </c>
       <c r="G2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -3387,19 +3381,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>148</v>
-      </c>
       <c r="F3" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -3407,19 +3401,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>149</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.35">
@@ -3427,14 +3421,14 @@
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -3442,19 +3436,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -3462,19 +3456,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -3482,19 +3476,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>164</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
@@ -3502,17 +3496,17 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>169</v>
-      </c>
-      <c r="C9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>170</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -3520,19 +3514,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D10" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="F10" s="10" t="s">
         <v>167</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.35">
@@ -3540,14 +3534,14 @@
         <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E11" s="9"/>
       <c r="F11" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -3555,19 +3549,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="F12" s="4" t="s">
         <v>174</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -3575,19 +3569,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C13" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="F13" s="4" t="s">
         <v>177</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -3595,19 +3589,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="F14" s="4" t="s">
         <v>180</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.35">
@@ -3615,16 +3609,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.35">

--- a/data/UoB_Agreements.xlsx
+++ b/data/UoB_Agreements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97333\Desktop\Hawra\Cloud Computing\ITCC481\Partnership\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C33CB9-5BF1-454E-A53A-457970A2376E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E764C3E4-C905-4821-BD5C-7171BAA642D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
